--- a/data/medicina/calendario.xlsx
+++ b/data/medicina/calendario.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Calendario" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Calendario'!$A$1:$J$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Calendario'!$A$1:$J$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -503,10 +503,10 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -575,12 +575,12 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -695,12 +695,12 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Control lógica 2, 15 min</t>
+          <t>Control lógica 2</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Control lógica 3, 15 min</t>
+          <t>Control lógica 3</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Sin actividades (semana mechona)</t>
+          <t>Repaso (semana mechona)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -871,12 +871,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Sin actividades (semana mechona)</t>
+          <t>Repaso (semana mechona)</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Control Modelos y Derivadas 2, 15 min</t>
+          <t>Control Modelos y Derivadas 2</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Control Modelos y Derivadas 3, 15 min</t>
+          <t>Control Modelos y Derivadas 3</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Control Modelos y Derivadas 4, 15 min</t>
+          <t>Control Modelos y Derivadas 4</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -1667,7 +1667,11 @@
           <t>JCS</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>CONFLICTO: Bloque protegido 3</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1683,12 +1687,12 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1723,12 +1727,12 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -1753,7 +1757,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Control Trigonometría y Vectores 2, 15 min</t>
+          <t>Control Trigonometría y Vectores 2</t>
         </is>
       </c>
     </row>
@@ -1771,12 +1775,12 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1811,12 +1815,12 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -1841,7 +1845,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Control Trigonometría y Vectores 3, 15 min</t>
+          <t>Control Trigonometría y Vectores 3</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1863,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1899,12 +1903,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -1947,12 +1951,12 @@
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -1991,12 +1995,12 @@
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -2035,12 +2039,12 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2075,12 +2079,12 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
@@ -2123,12 +2127,12 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>10:15–11:45</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2163,42 +2167,1678 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
+          <t>12:00–13:30</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>46099</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Lógica 1</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>46100</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
           <t>08:30–10:00</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>Sección 2</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Seminario</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Lógica 1</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>46106</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Lógica 2</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Lógica 2</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Control lógica 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Lógica 3</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Lógica 3</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Control lógica 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>46120</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Repaso (semana mechona)</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>46121</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Repaso (semana mechona)</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>46127</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 1</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>46128</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Certamen 1</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Certamen 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>46134</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Modelos y Derivadas 1</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>46135</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Modelos y Derivadas 1</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>46141</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Modelos y Derivadas 2</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>46148</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>46149</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>46155</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Semana Receso</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B59" s="10" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>Sin clases (Feriado)</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>Semana Receso</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr"/>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>Día de las Glorias Navales</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Linealización de modelos</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Linealización de modelos</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>Trabajo práctico</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Trabajo Práctico</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>46183</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Trigonometría y Vectores 1</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Trigonometría y Vectores 1</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr"/>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 3</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Certamen 3</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Certamen 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B72" s="13" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>Trabajo autónomo</t>
+        </is>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>Trabajo Autónomo</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="inlineStr"/>
+      <c r="I72" s="12" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J72" s="12" t="inlineStr">
+        <is>
+          <t>No hay clases (trabajo autónomo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B73" s="13" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>Trabajo autónomo</t>
+        </is>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>Trabajo Autónomo</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="inlineStr"/>
+      <c r="I73" s="12" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J73" s="12" t="inlineStr">
+        <is>
+          <t>No hay clases (trabajo autónomo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B75" s="10" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>Sin clases (Feriado)</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>Examen Primera Oportunidad</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="inlineStr">
+        <is>
+          <t>Virgen del Carmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Clase teórica</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>Examen Segunda Oportunidad</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>08:30–10:00</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Sección 2</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Examen Segunda Oportunidad</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>Examen</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I77" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J77" s="5" t="inlineStr">
         <is>
           <t>Examen 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J39"/>
+  <autoFilter ref="A1:J77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/medicina/calendario.xlsx
+++ b/data/medicina/calendario.xlsx
@@ -503,7 +503,7 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
@@ -846,7 +846,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Repaso (semana mechona)</t>
+          <t>Modelos y Derivadas 1</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Repaso (semana mechona)</t>
+          <t>Sin Seminario (semana mechona)</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
+          <t>Modelos y Derivadas 1 y Revisión Certamen 1</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 1</t>
+          <t>Modelos y Derivadas 2</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 1</t>
+          <t>Modelos y Derivadas 2</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 2</t>
+          <t>Modelos y Derivadas 3</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 2</t>
+          <t>Modelos y Derivadas 3</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 3</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 3</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Modelos y Derivadas 5</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Modelos y Derivadas 5</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Certamen 2</t>
+          <t>Teórico Linealización de Modelos</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Linealización de modelos</t>
+          <t>Revisión Certamen 2</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Certamen 3</t>
+          <t>Sin Actividad (semana de certamen 3)</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Trabajo Autónomo</t>
+          <t>Revisión Certamen 3</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Repaso (semana mechona)</t>
+          <t>Modelos y Derivadas 1</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Repaso (semana mechona)</t>
+          <t>Sin Seminario (semana mechona)</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr"/>
@@ -2569,13 +2569,21 @@
           <t>Certamen 1</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 1</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -2606,24 +2614,16 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
-        </is>
-      </c>
-      <c r="H49" s="8" t="inlineStr">
-        <is>
-          <t>Certamen</t>
-        </is>
-      </c>
+          <t>Modelos y Derivadas 1 y Revisión Certamen 1</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 1</t>
-        </is>
-      </c>
+      <c r="J49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 1</t>
+          <t>Modelos y Derivadas 2</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 1</t>
+          <t>Modelos y Derivadas 2</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr"/>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 2</t>
+          <t>Modelos y Derivadas 3</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 2</t>
+          <t>Modelos y Derivadas 3</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 3</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 3</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Modelos y Derivadas 5</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Modelos y Derivadas 5</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -3085,13 +3085,21 @@
           <t>Certamen 2</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
@@ -3122,24 +3130,16 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Certamen 2</t>
-        </is>
-      </c>
-      <c r="H61" s="8" t="inlineStr">
-        <is>
-          <t>Certamen</t>
-        </is>
-      </c>
+          <t>Teórico Linealización de Modelos</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 2</t>
-        </is>
-      </c>
+      <c r="J61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Linealización de modelos</t>
+          <t>Revisión Certamen 2</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3517,13 +3517,21 @@
           <t>Certamen 3</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr"/>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 3</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
@@ -3554,24 +3562,16 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Certamen 3</t>
-        </is>
-      </c>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>Certamen</t>
-        </is>
-      </c>
+          <t>Sin Actividad (semana de certamen 3)</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 3</t>
-        </is>
-      </c>
+      <c r="J71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>Trabajo Autónomo</t>
+          <t>Revisión Certamen 3</t>
         </is>
       </c>
       <c r="H73" s="12" t="inlineStr"/>
@@ -3693,13 +3693,21 @@
           <t>Examen Primera Oportunidad</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="9" t="n">
@@ -3733,11 +3741,7 @@
           <t>Examen Primera Oportunidad</t>
         </is>
       </c>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>Examen</t>
-        </is>
-      </c>
+      <c r="H75" s="9" t="inlineStr"/>
       <c r="I75" s="9" t="inlineStr">
         <is>
           <t>JCS</t>
@@ -3781,13 +3785,21 @@
           <t>Examen Segunda Oportunidad</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr"/>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
@@ -3821,21 +3833,13 @@
           <t>Examen Segunda Oportunidad</t>
         </is>
       </c>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Examen</t>
-        </is>
-      </c>
+      <c r="H77" s="5" t="inlineStr"/>
       <c r="I77" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t>Examen 2</t>
-        </is>
-      </c>
+      <c r="J77" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J77"/>

--- a/data/medicina/calendario.xlsx
+++ b/data/medicina/calendario.xlsx
@@ -505,7 +505,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -596,7 +596,7 @@
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -636,7 +636,7 @@
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr"/>
@@ -676,7 +676,7 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -720,7 +720,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -764,7 +764,7 @@
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -808,7 +808,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -852,7 +852,7 @@
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -892,7 +892,7 @@
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr"/>
@@ -932,7 +932,7 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -976,7 +976,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1020,7 +1020,7 @@
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
@@ -1100,7 +1100,7 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1188,7 +1188,7 @@
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1276,7 +1276,7 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1364,7 +1364,7 @@
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1404,7 +1404,7 @@
       <c r="H21" s="9" t="inlineStr"/>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
@@ -1448,7 +1448,7 @@
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1536,7 +1536,7 @@
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1624,7 +1624,7 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -1664,7 +1664,7 @@
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -1708,7 +1708,7 @@
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -1884,7 +1884,7 @@
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -1972,7 +1972,7 @@
       <c r="H34" s="12" t="inlineStr"/>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J34" s="12" t="inlineStr">
@@ -2016,7 +2016,7 @@
       <c r="H35" s="12" t="inlineStr"/>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
@@ -2060,7 +2060,7 @@
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
@@ -2148,7 +2148,7 @@
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -2276,7 +2276,7 @@
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr"/>
@@ -2316,7 +2316,7 @@
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -2492,7 +2492,7 @@
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -2532,7 +2532,7 @@
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr"/>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -2620,7 +2620,7 @@
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr"/>
@@ -2660,7 +2660,7 @@
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -2700,7 +2700,7 @@
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr"/>
@@ -2740,7 +2740,7 @@
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
@@ -2828,7 +2828,7 @@
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
@@ -2916,7 +2916,7 @@
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
@@ -3004,7 +3004,7 @@
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -3044,7 +3044,7 @@
       <c r="H59" s="9" t="inlineStr"/>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J59" s="9" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -3136,7 +3136,7 @@
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr"/>
@@ -3176,7 +3176,7 @@
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
@@ -3264,7 +3264,7 @@
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -3304,7 +3304,7 @@
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
@@ -3432,7 +3432,7 @@
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       <c r="H71" s="5" t="inlineStr"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr"/>
@@ -3608,7 +3608,7 @@
       <c r="H72" s="12" t="inlineStr"/>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J72" s="12" t="inlineStr">
@@ -3652,7 +3652,7 @@
       <c r="H73" s="12" t="inlineStr"/>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J73" s="12" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
       <c r="H75" s="9" t="inlineStr"/>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J75" s="9" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       <c r="H77" s="5" t="inlineStr"/>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR, JCS, TY, XX</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr"/>

--- a/data/medicina/calendario.xlsx
+++ b/data/medicina/calendario.xlsx
@@ -636,7 +636,7 @@
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr"/>
@@ -720,7 +720,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -892,7 +892,7 @@
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr"/>
@@ -976,7 +976,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1060,7 +1060,7 @@
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1404,7 +1404,7 @@
       <c r="H21" s="9" t="inlineStr"/>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1664,7 +1664,7 @@
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -2016,7 +2016,7 @@
       <c r="H35" s="12" t="inlineStr"/>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -2276,7 +2276,7 @@
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr"/>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -2532,7 +2532,7 @@
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr"/>
@@ -2620,7 +2620,7 @@
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr"/>
@@ -2700,7 +2700,7 @@
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr"/>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
@@ -3044,7 +3044,7 @@
       <c r="H59" s="9" t="inlineStr"/>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J59" s="9" t="inlineStr">
@@ -3136,7 +3136,7 @@
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr"/>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
@@ -3304,7 +3304,7 @@
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr"/>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
@@ -3568,7 +3568,7 @@
       <c r="H71" s="5" t="inlineStr"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr"/>
@@ -3652,7 +3652,7 @@
       <c r="H73" s="12" t="inlineStr"/>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J73" s="12" t="inlineStr">
@@ -3744,7 +3744,7 @@
       <c r="H75" s="9" t="inlineStr"/>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J75" s="9" t="inlineStr">
@@ -3836,7 +3836,7 @@
       <c r="H77" s="5" t="inlineStr"/>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>AR, JCS, TY, XX</t>
+          <t>TY, JCS, AR, XX</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr"/>

--- a/data/medicina/calendario.xlsx
+++ b/data/medicina/calendario.xlsx
@@ -636,7 +636,7 @@
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr"/>
@@ -720,7 +720,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -892,7 +892,7 @@
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr"/>
@@ -976,7 +976,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1060,7 +1060,7 @@
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1404,7 +1404,7 @@
       <c r="H21" s="9" t="inlineStr"/>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1664,7 +1664,7 @@
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -2016,7 +2016,7 @@
       <c r="H35" s="12" t="inlineStr"/>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -2276,7 +2276,7 @@
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr"/>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -2532,7 +2532,7 @@
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr"/>
@@ -2620,7 +2620,7 @@
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr"/>
@@ -2700,7 +2700,7 @@
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr"/>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
@@ -3044,7 +3044,7 @@
       <c r="H59" s="9" t="inlineStr"/>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J59" s="9" t="inlineStr">
@@ -3136,7 +3136,7 @@
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr"/>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
@@ -3304,7 +3304,7 @@
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr"/>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
@@ -3568,7 +3568,7 @@
       <c r="H71" s="5" t="inlineStr"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr"/>
@@ -3652,7 +3652,7 @@
       <c r="H73" s="12" t="inlineStr"/>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J73" s="12" t="inlineStr">
@@ -3744,7 +3744,7 @@
       <c r="H75" s="9" t="inlineStr"/>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J75" s="9" t="inlineStr">
@@ -3836,7 +3836,7 @@
       <c r="H77" s="5" t="inlineStr"/>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr"/>

--- a/data/medicina/calendario.xlsx
+++ b/data/medicina/calendario.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Calendario" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Calendario'!$A$1:$J$77</definedName>
